--- a/Result/profitability/2705.xlsx
+++ b/Result/profitability/2705.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1375</v>
+        <v>0.08874999999999995</v>
       </c>
       <c r="N2" t="n">
-        <v>33.64125</v>
+        <v>32.46</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06375000000000004</v>
+        <v>-0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>33.3175</v>
+        <v>31.4925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.16</v>
+        <v>-0.16125</v>
       </c>
       <c r="N4" t="n">
-        <v>32.87375</v>
+        <v>32.62</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14625</v>
+        <v>-0.165</v>
       </c>
       <c r="N5" t="n">
-        <v>33.8425</v>
+        <v>33.42625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,16 +1137,16 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.15125</v>
+        <v>-0.16625</v>
       </c>
       <c r="N6" t="n">
-        <v>33.85875</v>
+        <v>33.41375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.18125</v>
+        <v>-0.37625</v>
       </c>
       <c r="N7" t="n">
-        <v>33.00375</v>
+        <v>31.4175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3375</v>
+        <v>-0.3412500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>33.11875</v>
+        <v>32.9425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3225000000000001</v>
+        <v>-0.3225</v>
       </c>
       <c r="N9" t="n">
         <v>34.22</v>
@@ -1645,7 +1645,7 @@
         <v>-0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2887500000000001</v>
+        <v>-0.28875</v>
       </c>
       <c r="N10" t="n">
         <v>34.6975</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>527</v>
+      </c>
+      <c r="D75" t="n">
+        <v>385</v>
+      </c>
+      <c r="E75" t="n">
+        <v>141</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.74375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04987619384506548</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.330000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1103014243126864</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
